--- a/out/LSTM-Mamba1_repeat_1_000008.xlsx
+++ b/out/LSTM-Mamba1_repeat_1_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.138476860958186</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
-        <v>-7.40318342417013e-05</v>
+        <v>-9.028927320521324e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.08504835841919102</v>
+        <v>-0.1037250332593648</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.08512239025343268</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.08512239025343268</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.08512239025343268</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.08512239025343268</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.08512239025343268</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.08512239025343268</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.08512239025343268</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.08512239025343268</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.08512239025343268</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.08512239025343268</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.08512239025343268</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.08512239025343268</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.08512239025343268</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.08518760456241783</v>
+        <v>-0.1038953169789104</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.2344958031643013</v>
+        <v>0.2876418110555966</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.3842542422952026</v>
+        <v>0.4719405879425919</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.01670777674167397</v>
+        <v>0.02049438205934407</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1827978356073662</v>
+        <v>0.2248262053035155</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.02929974771260294</v>
+        <v>0.03594029158310495</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2246839785178253</v>
+        <v>0.2762054937622342</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.03559542141153378</v>
+        <v>0.04366320975871988</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.266572909890468</v>
+        <v>0.3275882019587611</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.009418660111584614</v>
+        <v>0.01155418788124789</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2497696836617778</v>
+        <v>0.3069779783840266</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.005230638457325624</v>
+        <v>0.006417104351165654</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2508048203046597</v>
+        <v>0.3082488606887963</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01099298294661256</v>
+        <v>0.01348698945083388</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.2675673899644611</v>
+        <v>0.3288123602160108</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.004316110691554126</v>
+        <v>0.005294658180000239</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2651964510959743</v>
+        <v>0.3259053062485033</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.003072284281149243</v>
+        <v>0.003769158075759273</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2670231084982925</v>
+        <v>0.3281472705010839</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.00120623894937027</v>
+        <v>0.001480532971537081</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.266360907129416</v>
+        <v>0.3273358735346063</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0006824702724862232</v>
+        <v>0.0008381530023541796</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.266518902926605</v>
+        <v>0.3275309646785506</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.000256884338442024</v>
+        <v>0.0003167771692067918</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2663496517538678</v>
+        <v>0.3273241493362637</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001172066092191951</v>
+        <v>0.0001458315807480156</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2663280960579635</v>
+        <v>0.3272988064421003</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>4.021021648382256e-05</v>
+        <v>4.989812001607026e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.2662901054838479</v>
+        <v>0.3272534524713112</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>8.355601046452064e-06</v>
+        <v>1.121751555640607e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2662665633939921</v>
+        <v>0.3272256063400598</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>1.677800523226032e-06</v>
+        <v>3.108757778203038e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2662615529690036</v>
+        <v>0.3272205936811452</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-1.404168982957566e-06</v>
+        <v>-3.767886923740136e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2662570619267074</v>
+        <v>0.3272162480553358</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-2.908363659633048e-06</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.2662533450962277</v>
+        <v>0.3272128977005431</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2662480492662236</v>
+        <v>0.3272075283735553</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2662423872692198</v>
+        <v>0.3272015356401249</v>
       </c>
     </row>
     <row r="80">
@@ -64533,7 +64533,7 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>0</v>
+        <v>-4.890058184668745e-06</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2662422035267607</v>
+        <v>0.3271961678515465</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2662422402752524</v>
+        <v>0.3271962046000382</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2662423505207279</v>
+        <v>0.3271963148455138</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2662424240177115</v>
+        <v>0.3271963883424974</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2662426077601707</v>
+        <v>0.3271965720849566</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2662441511968272</v>
+        <v>0.327198115521613</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2662456211365002</v>
+        <v>0.3271995854612861</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2662468705852223</v>
+        <v>0.3272008349100081</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2662482302794196</v>
+        <v>0.3272021946042054</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2662460253699103</v>
+        <v>0.3271999896946962</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2662456211365002</v>
+        <v>0.3271995854612861</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2662447759211883</v>
+        <v>0.3271987402459742</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2662453271485656</v>
+        <v>0.3271992914733514</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2662449964121392</v>
+        <v>0.327198960736925</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2662447024242047</v>
+        <v>0.3271986667489906</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2662447759211883</v>
+        <v>0.3271987402459742</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2662443349392863</v>
+        <v>0.3271982992640722</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2662442246938108</v>
+        <v>0.3271981890185967</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2662441879453191</v>
+        <v>0.327198152270105</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2662443349392863</v>
+        <v>0.3271982992640722</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2662438572088927</v>
+        <v>0.3271978215336785</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.26624481266968</v>
+        <v>0.3271987769944659</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2662447759211883</v>
+        <v>0.3271987402459742</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2662444451847619</v>
+        <v>0.3271984095095478</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.2662448861666639</v>
+        <v>0.3271988504914497</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2662442614423027</v>
+        <v>0.3271982257670886</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2662440776998435</v>
+        <v>0.3271980420246294</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2662436734664335</v>
+        <v>0.3271976377912194</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2662428282511216</v>
+        <v>0.3271967925759074</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2662427915026299</v>
+        <v>0.3271967558274158</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2662429384965971</v>
+        <v>0.327196902821383</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2662428649996135</v>
+        <v>0.3271968293243994</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2662429384965971</v>
+        <v>0.327196902821383</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2662429752450891</v>
+        <v>0.3271969395698749</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2662428649996135</v>
+        <v>0.3271968293243994</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2662433059815155</v>
+        <v>0.3271972703063013</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2662431957360399</v>
+        <v>0.3271971600608258</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.266243158987548</v>
+        <v>0.3271971233123338</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2662430854905644</v>
+        <v>0.3271970498153502</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2662430487420727</v>
+        <v>0.3271970130668585</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2662428282511216</v>
+        <v>0.3271967925759074</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2662427547541379</v>
+        <v>0.3271967190789238</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2662426812571543</v>
+        <v>0.3271966455819402</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2662427180056463</v>
+        <v>0.3271966823304321</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2662426077601707</v>
+        <v>0.3271965720849566</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2662427180056463</v>
+        <v>0.3271966823304321</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2662430119935807</v>
+        <v>0.3271969763183666</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_1_000008.xlsx
+++ b/out/LSTM-Mamba1_repeat_1_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.037571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.037571854792519</v>
+        <v>0.8369524225432805</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716907</v>
       </c>
       <c r="JC45" t="n">
-        <v>-7.40318342417013e-05</v>
+        <v>-0.0001025316694092471</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.08504835841919102</v>
+        <v>-0.1177891951288304</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.08512239025343268</v>
+        <v>-0.1178917267982396</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.08512239025343268</v>
+        <v>-0.1178917267982396</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.08512239025343268</v>
+        <v>-0.1178917267982396</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.08512239025343268</v>
+        <v>-0.1178917267982396</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.08512239025343268</v>
+        <v>-0.1178917267982396</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.08512239025343268</v>
+        <v>-0.1178917267982396</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.08512239025343268</v>
+        <v>-0.1178917267982396</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.08512239025343268</v>
+        <v>-0.1178917267982396</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.08512239025343268</v>
+        <v>-0.1178917267982396</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.08512239025343268</v>
+        <v>-0.1178917267982396</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.08512239025343268</v>
+        <v>-0.1178917267982396</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.08512239025343268</v>
+        <v>-0.1178917267982396</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.08512239025343268</v>
+        <v>-0.1178917267982396</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.08518760456241783</v>
+        <v>-0.1179662541831741</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.2344958031643013</v>
+        <v>0.2679832465659846</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.3842542422952026</v>
+        <v>0.4185152910742976</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.01670777674167397</v>
+        <v>0.01909378663942246</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1827978356073662</v>
+        <v>0.1882892289287678</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.02929974771260294</v>
+        <v>0.03348399610930496</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2246839785178253</v>
+        <v>0.2361570624679737</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.03559542141153378</v>
+        <v>0.04067878905771256</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.266572909890468</v>
+        <v>0.2840280826028176</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.009418660111584614</v>
+        <v>0.01076442560155795</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2497696836617778</v>
+        <v>0.264825950547341</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.005230638457325624</v>
+        <v>0.005978324756535884</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2508048203046597</v>
+        <v>0.2660096260787512</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01099298294661256</v>
+        <v>0.01256368296379521</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.2675673899644611</v>
+        <v>0.2851667234454225</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.004316110691554126</v>
+        <v>0.004932547166330205</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2651964510959743</v>
+        <v>0.2824579362160531</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.003072284281149243</v>
+        <v>0.003512142740618445</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2670231084982925</v>
+        <v>0.2845464056349583</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.00120623894937027</v>
+        <v>0.001378691131623661</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.266360907129416</v>
+        <v>0.2837902666311106</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0006824702724862232</v>
+        <v>0.0007811207151748292</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.266518902926605</v>
+        <v>0.2839716519597347</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.000256884338442024</v>
+        <v>0.0002944641538238391</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2663496517538678</v>
+        <v>0.2837788311119862</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001172066092191951</v>
+        <v>0.0001348219763138539</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2663280960579635</v>
+        <v>0.2837548996036246</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>4.021021648382256e-05</v>
+        <v>4.666881883865436e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.2662901054838479</v>
+        <v>0.2837121960903499</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>8.355601046452064e-06</v>
+        <v>1.026354405308807e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2662665633939921</v>
+        <v>0.2836860051305147</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>1.677800523226032e-06</v>
+        <v>2.631772026544036e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2662615529690036</v>
+        <v>0.283680993216242</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-1.404168982957566e-06</v>
+        <v>-8.904788376657899e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2662570619267074</v>
+        <v>0.2836765748821893</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-2.908363659633048e-06</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.2662533450962277</v>
+        <v>0.2836730407849373</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2662480492662236</v>
+        <v>0.2836677449549332</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2662423872692198</v>
+        <v>0.2836620829579294</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2662422035267607</v>
+        <v>0.2836618992154703</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2662422402752524</v>
+        <v>0.283661935963962</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2662423505207279</v>
+        <v>0.2836620462094375</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2662424240177115</v>
+        <v>0.2836621197064211</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2662426077601707</v>
+        <v>0.2836623034488803</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2662441511968272</v>
+        <v>0.2836638468855368</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2662456211365002</v>
+        <v>0.2836653168252099</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2662468705852223</v>
+        <v>0.2836665662739319</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2662482302794196</v>
+        <v>0.2836679259681292</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2662460253699103</v>
+        <v>0.2836657210586199</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2662456211365002</v>
+        <v>0.2836653168252099</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2662447759211883</v>
+        <v>0.2836644716098979</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2662453271485656</v>
+        <v>0.2836650228372752</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2662449964121392</v>
+        <v>0.2836646921008488</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2662447024242047</v>
+        <v>0.2836643981129143</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2662447759211883</v>
+        <v>0.2836644716098979</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2662443349392863</v>
+        <v>0.2836640306279959</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2662442246938108</v>
+        <v>0.2836639203825204</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2662441879453191</v>
+        <v>0.2836638836340287</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2662443349392863</v>
+        <v>0.2836640306279959</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2662438572088927</v>
+        <v>0.2836635528976023</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.26624481266968</v>
+        <v>0.2836645083583896</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2662447759211883</v>
+        <v>0.2836644716098979</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2662444451847619</v>
+        <v>0.2836641408734715</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.2662448861666639</v>
+        <v>0.2836645818553735</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2662442614423027</v>
+        <v>0.2836639571310123</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2662440776998435</v>
+        <v>0.2836637733885532</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2662436734664335</v>
+        <v>0.2836633691551432</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2662428282511216</v>
+        <v>0.2836625239398312</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2662427915026299</v>
+        <v>0.2836624871913395</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2662429384965971</v>
+        <v>0.2836626341853067</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2662428649996135</v>
+        <v>0.2836625606883231</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2662429384965971</v>
+        <v>0.2836626341853067</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2662429752450891</v>
+        <v>0.2836626709337987</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2662428649996135</v>
+        <v>0.2836625606883231</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2662433059815155</v>
+        <v>0.2836630016702251</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2662431957360399</v>
+        <v>0.2836628914247495</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.266243158987548</v>
+        <v>0.2836628546762576</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2662430854905644</v>
+        <v>0.283662781179274</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2662430487420727</v>
+        <v>0.2836627444307823</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2662428282511216</v>
+        <v>0.2836625239398312</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2662427547541379</v>
+        <v>0.2836624504428475</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2662426812571543</v>
+        <v>0.2836623769458639</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2662427180056463</v>
+        <v>0.2836624136943559</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2662426077601707</v>
+        <v>0.2836623034488803</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2662427180056463</v>
+        <v>0.2836624136943559</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2662430119935807</v>
+        <v>0.2836627076822903</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_1_000008.xlsx
+++ b/out/LSTM-Mamba1_repeat_1_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.007318066898733377</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-1.14</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.004063189029693604</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.7199999999999996</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.002224505878984928</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.001450002193450928</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.001143680885434151</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.0009167725220322609</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.0006880946457386017</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.0005021039396524429</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.0003042612224817276</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.0001208139583468437</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>7.881596684455872e-05</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.036952422543281</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.0001991791650652885</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.762906414714871</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.00029770378023386</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.762906414714871</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.0003463085740804672</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.762906414714871</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.0003540515899658203</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.762906414714871</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.0003016740083694458</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.762906414714871</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.0003086617216467857</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.762906414714871</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.0003777472302317619</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.762906414714871</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.000494055449962616</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.762906414714871</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.0006234971806406975</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.762906414714871</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.000726005993783474</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.56290641471487</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.0008454779163002968</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.56290641471487</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.0009346548467874527</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.56290641471487</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.001020879484713078</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.56290641471487</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.001039552502334118</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.56290641471487</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.001075685955584049</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.56290641471487</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.001110970042645931</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.56290641471487</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.001168462447822094</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.56290641471487</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.001214789226651192</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.56290641471487</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.001243789680302143</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.56290641471487</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.001251112669706345</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.56290641471487</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.001077950932085514</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.56290641471487</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.0009791357442736626</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.56290641471487</v>
+        <v>-0.16</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.0009149964898824692</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.56290641471487</v>
+        <v>-0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.0008514886721968651</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.56290641471487</v>
+        <v>-0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.0008704084903001785</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.56290641471487</v>
+        <v>-0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.0008456241339445114</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.56290641471487</v>
+        <v>-0.3</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.0008367039263248444</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.56290641471487</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.0008651530370116234</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.56290641471487</v>
+        <v>-0.3</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.0008062729611992836</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.56290641471487</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.0006966171786189079</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.56290641471487</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.0005365703254938126</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.56290641471487</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.0003027049824595451</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.8369524225432805</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.0002329479902982712</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.1109984303716907</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001025316694092471</v>
+        <v>-7.719068296707701e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1177891951288304</v>
+        <v>-0.08867726889193431</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.0008797431364655495</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1178917267982396</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.001145084388554096</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1178917267982396</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.001331719569861889</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1178917267982396</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.001316921785473824</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1178917267982396</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.001242233440279961</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1178917267982396</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.001092112623155117</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1178917267982396</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.0009609805420041084</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1178917267982396</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.0008073551580309868</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1178917267982396</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.0007621906697750092</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1178917267982396</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.0007603270933032036</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1178917267982396</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.0008146781474351883</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1178917267982396</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.0008920226246118546</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1178917267982396</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.000974997878074646</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1178917267982396</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.001090390607714653</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1179662541831741</v>
+        <v>-0.08882259802308166</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.2679832465659846</v>
+        <v>0.2450100850180599</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.001434708014130592</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4185152910742976</v>
+        <v>0.4016685148271203</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.01909378663942246</v>
+        <v>0.01745691711621853</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.001646985299885273</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1882892289287678</v>
+        <v>0.191178799990556</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.03348399610930496</v>
+        <v>0.03061348468161163</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.001814977265894413</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2361570624679737</v>
+        <v>0.2349432102014082</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.04067878905771256</v>
+        <v>0.03719176846430827</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.002102645114064217</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.2840280826028176</v>
+        <v>0.2787107170440257</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01076442560155795</v>
+        <v>0.009841275378308329</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.002297542057931423</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.264825950547341</v>
+        <v>0.2611541543437242</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.005978324756535884</v>
+        <v>0.005465436902612457</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.002303945831954479</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2660096260787512</v>
+        <v>0.2622359371537592</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01256368296379521</v>
+        <v>0.01148623516005559</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.002632901072502136</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.2851667234454225</v>
+        <v>0.2797504684094372</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.004932547166330205</v>
+        <v>0.004509882471444446</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.003037373535335064</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2824579362160531</v>
+        <v>0.2772734336275656</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.003512142740618445</v>
+        <v>0.00321027909196311</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.003549625165760517</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2845464056349583</v>
+        <v>0.2791822281331267</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001378691131623661</v>
+        <v>0.001260554597324094</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.003863661549985409</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2837902666311106</v>
+        <v>0.2784905558508476</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0007811207151748292</v>
+        <v>0.0007132985358264126</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.00413108803331852</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2839716519597347</v>
+        <v>0.27865586087661</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0002944641538238391</v>
+        <v>0.0002686280307488412</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.00421525165438652</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2837788311119862</v>
+        <v>0.2784792441804321</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001348219763138539</v>
+        <v>0.000122711411436276</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.004166276194155216</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2837548996036246</v>
+        <v>0.2784569460431346</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>4.666881883865436e-05</v>
+        <v>4.182486707253051e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.003965079784393311</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.2837121960903499</v>
+        <v>0.278417483246295</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.026354405308807e-05</v>
+        <v>8.832586798111064e-06</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.003640576265752316</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2836860051305147</v>
+        <v>0.2783929482025178</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>2.631772026544036e-06</v>
+        <v>2.154786274885033e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.00332386139780283</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.283680993216242</v>
+        <v>0.278387937032887</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-8.904788376657899e-07</v>
+        <v>-1.404168982957566e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.003071962855756283</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2836765748821893</v>
+        <v>0.2783834827390828</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.002975260838866234</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.2836730407849373</v>
+        <v>0.2783799486418308</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.002911835908889771</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2836677449549332</v>
+        <v>0.2783746528118267</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.002765683457255363</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2836620829579294</v>
+        <v>0.278368990814823</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.002567697316408157</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2836618992154703</v>
+        <v>0.2783688070723638</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.002378742210566998</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.3</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.283661935963962</v>
+        <v>0.2783688438208555</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.002262231893837452</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2836620462094375</v>
+        <v>0.2783689540663311</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.00222503300756216</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2836621197064211</v>
+        <v>0.2783690275633147</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.002213777974247932</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2836623034488803</v>
+        <v>0.2783692113057738</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.002527652308344841</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2836638468855368</v>
+        <v>0.2783707547424303</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.003356304951012135</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2836653168252099</v>
+        <v>0.2783722246821034</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.004439240321516991</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2836665662739319</v>
+        <v>0.2783734741308254</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.005383648909628391</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2836679259681292</v>
+        <v>0.2783748338250227</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.006494957488030195</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2836657210586199</v>
+        <v>0.2783726289155134</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.007154522463679314</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2836653168252099</v>
+        <v>0.2783722246821034</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.007391102146357298</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2836644716098979</v>
+        <v>0.2783713794667914</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.007536919321864843</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2836650228372752</v>
+        <v>0.2783719306941687</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.007521296385675669</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2836646921008488</v>
+        <v>0.2783715999577422</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.007311701774597168</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2836643981129143</v>
+        <v>0.2783713059698078</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.007117477711290121</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2836644716098979</v>
+        <v>0.2783713794667914</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.006799006368964911</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2836640306279959</v>
+        <v>0.2783709384848895</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.006469596643000841</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2836639203825204</v>
+        <v>0.2783708282394139</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.006149512715637684</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2836638836340287</v>
+        <v>0.2783707914909222</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.005935132969170809</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2836640306279959</v>
+        <v>0.2783709384848895</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.005555046256631613</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2836635528976023</v>
+        <v>0.2783704607544958</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.005537450779229403</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2836645083583896</v>
+        <v>0.2783714162152831</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.005824857391417027</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2836644716098979</v>
+        <v>0.2783713794667914</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.006007816642522812</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2836641408734715</v>
+        <v>0.278371048730365</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.006147948559373617</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.2836645818553735</v>
+        <v>0.2783714897122669</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.006127240601927042</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2836639571310123</v>
+        <v>0.2783708649879058</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.00593393063172698</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2836637733885532</v>
+        <v>0.2783706812454467</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.005631275475025177</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.16</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2836633691551432</v>
+        <v>0.2783702770120366</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.00512311514467001</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2836625239398312</v>
+        <v>0.2783694317967247</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.004563000053167343</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2836624871913395</v>
+        <v>0.278369395048233</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.00413472019135952</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2836626341853067</v>
+        <v>0.2783695420422002</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.00381704606115818</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2836625606883231</v>
+        <v>0.2783694685452166</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.003558513708412647</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2836626341853067</v>
+        <v>0.2783695420422002</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.003508126363158226</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2836626709337987</v>
+        <v>0.2783695787906921</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.003403455018997192</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2836625606883231</v>
+        <v>0.2783694685452166</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.003490455448627472</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2836630016702251</v>
+        <v>0.2783699095271185</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.003546088002622128</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2836628914247495</v>
+        <v>0.278369799281643</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.003596251830458641</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2836628546762576</v>
+        <v>0.2783697625331511</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.003583973273634911</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.283662781179274</v>
+        <v>0.2783696890361674</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.0035344073548913</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2836627444307823</v>
+        <v>0.2783696522876757</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.00342289824038744</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2836625239398312</v>
+        <v>0.2783694317967247</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.003249894827604294</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2836624504428475</v>
+        <v>0.2783693582997411</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.003088707104325294</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2836623769458639</v>
+        <v>0.2783692848027574</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.002971240319311619</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2836624136943559</v>
+        <v>0.2783693215512494</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.002829342149198055</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2836623034488803</v>
+        <v>0.2783692113057738</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.002738972194492817</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2836624136943559</v>
+        <v>0.2783693215512494</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.002815459854900837</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2836627076822903</v>
+        <v>0.2783696155391838</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_1_000008.xlsx
+++ b/out/LSTM-Mamba1_repeat_1_000008.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.007318066898733377</v>
+        <v>-0.007318069692701101</v>
       </c>
       <c r="JB2" t="n">
         <v>-1.14</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.004063189029693604</v>
+        <v>-0.004063192754983902</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.7199999999999996</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.002224505878984928</v>
+        <v>-0.002224503085017204</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.3</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.001450002193450928</v>
+        <v>-0.001450016163289547</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.02000000000000007</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.001143680885434151</v>
+        <v>-0.001143687404692173</v>
       </c>
       <c r="JB6" t="n">
         <v>0.8599999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.0009167725220322609</v>
+        <v>-0.000916777178645134</v>
       </c>
       <c r="JB7" t="n">
         <v>0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.0006880946457386017</v>
+        <v>-0.0006880676373839378</v>
       </c>
       <c r="JB8" t="n">
         <v>0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.0005021039396524429</v>
+        <v>-0.0005021058022975922</v>
       </c>
       <c r="JB9" t="n">
         <v>0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.0003042612224817276</v>
+        <v>-0.0003042649477720261</v>
       </c>
       <c r="JB10" t="n">
         <v>0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.0001208139583468437</v>
+        <v>-0.0001208102330565453</v>
       </c>
       <c r="JB11" t="n">
         <v>0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>7.881596684455872e-05</v>
+        <v>7.881037890911102e-05</v>
       </c>
       <c r="JB12" t="n">
         <v>0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.0001991791650652885</v>
+        <v>0.0001991679891943932</v>
       </c>
       <c r="JB13" t="n">
         <v>0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.00029770378023386</v>
+        <v>0.0002976851537823677</v>
       </c>
       <c r="JB14" t="n">
         <v>0.9999999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.0003463085740804672</v>
+        <v>0.0003462955355644226</v>
       </c>
       <c r="JB15" t="n">
         <v>0.9999999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.0003540515899658203</v>
+        <v>0.0003540404140949249</v>
       </c>
       <c r="JB16" t="n">
         <v>0.3999999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.0003016740083694458</v>
+        <v>0.0003016702830791473</v>
       </c>
       <c r="JB17" t="n">
         <v>0.3999999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.0003086617216467857</v>
+        <v>0.0003086254000663757</v>
       </c>
       <c r="JB18" t="n">
         <v>0.3999999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.0003777472302317619</v>
+        <v>0.0003777192905545235</v>
       </c>
       <c r="JB19" t="n">
         <v>0.3999999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.000494055449962616</v>
+        <v>0.0004940461367368698</v>
       </c>
       <c r="JB20" t="n">
         <v>0.3999999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.0006234971806406975</v>
+        <v>0.000623481348156929</v>
       </c>
       <c r="JB21" t="n">
         <v>0.3999999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.000726005993783474</v>
+        <v>0.0007260004058480263</v>
       </c>
       <c r="JB22" t="n">
         <v>0.3999999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.0008454779163002968</v>
+        <v>0.0008454658091068268</v>
       </c>
       <c r="JB23" t="n">
         <v>0.3999999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.0009346548467874527</v>
+        <v>0.0009346241131424904</v>
       </c>
       <c r="JB24" t="n">
         <v>0.3999999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.001020879484713078</v>
+        <v>0.001020836643874645</v>
       </c>
       <c r="JB25" t="n">
         <v>0.3999999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.001039552502334118</v>
+        <v>0.001039523631334305</v>
       </c>
       <c r="JB26" t="n">
         <v>0.3999999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.001075685955584049</v>
+        <v>0.001075656153261662</v>
       </c>
       <c r="JB27" t="n">
         <v>0.3999999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.001110970042645931</v>
+        <v>0.001110910438001156</v>
       </c>
       <c r="JB28" t="n">
         <v>0.3999999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.001168462447822094</v>
+        <v>0.00116843543946743</v>
       </c>
       <c r="JB29" t="n">
         <v>0.3999999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.001214789226651192</v>
+        <v>0.001214771531522274</v>
       </c>
       <c r="JB30" t="n">
         <v>0.3999999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.001243789680302143</v>
+        <v>0.001243787817656994</v>
       </c>
       <c r="JB31" t="n">
         <v>0.2599999999999998</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.001251112669706345</v>
+        <v>0.001251108944416046</v>
       </c>
       <c r="JB32" t="n">
         <v>0.1199999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.001077950932085514</v>
+        <v>0.001077921129763126</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.02000000000000007</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.0009791357442736626</v>
+        <v>0.0009790938347578049</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.16</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.0009149964898824692</v>
+        <v>0.0009149778634309769</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.3</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.0008514886721968651</v>
+        <v>0.0008514383807778358</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.3</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.0008704084903001785</v>
+        <v>0.0008703805506229401</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.3</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.0008456241339445114</v>
+        <v>0.0008456148207187653</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.3</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.0008367039263248444</v>
+        <v>0.000836692750453949</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.3</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.0008651530370116234</v>
+        <v>0.000865153968334198</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.3</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.0008062729611992836</v>
+        <v>0.0008062757551670074</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.4399999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.0006966171786189079</v>
+        <v>0.0006966153159737587</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.5799999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.0005365703254938126</v>
+        <v>0.0005365572869777679</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.7199999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.0003027049824595451</v>
+        <v>0.0003026919439435005</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.8599999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.0002329479902982712</v>
+        <v>-0.0002329666167497635</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.0008797431364655495</v>
+        <v>-0.000879751518368721</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.001145084388554096</v>
+        <v>-0.001145089045166969</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.001331719569861889</v>
+        <v>-0.001331722363829613</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.001316921785473824</v>
+        <v>-0.00131692923605442</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.001242233440279961</v>
+        <v>-0.001242239959537983</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.001092112623155117</v>
+        <v>-0.001092130318284035</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.0009609805420041084</v>
+        <v>-0.0009609926491975784</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.0008073551580309868</v>
+        <v>-0.0008073644712567329</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.0007621906697750092</v>
+        <v>-0.0007622018456459045</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.0007603270933032036</v>
+        <v>-0.0007603242993354797</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.0008920226246118546</v>
+        <v>-0.0008920244872570038</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.000974997878074646</v>
+        <v>-0.0009750006720423698</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.001090390607714653</v>
+        <v>-0.001090377569198608</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.001434708014130592</v>
+        <v>-0.001434698700904846</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.001646985299885273</v>
+        <v>-0.001646981574594975</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.002102645114064217</v>
+        <v>-0.002102634869515896</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.002297542057931423</v>
+        <v>-0.002297528088092804</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.002303945831954479</v>
+        <v>-0.002303936518728733</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.9999999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.002632901072502136</v>
+        <v>-0.002632877789437771</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.9999999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.003037373535335064</v>
+        <v>-0.003037352114915848</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.9999999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.003549625165760517</v>
+        <v>-0.003549604676663876</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.9999999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.003863661549985409</v>
+        <v>-0.003863651305437088</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.00413108803331852</v>
+        <v>-0.004131082445383072</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.00421525165438652</v>
+        <v>-0.004215226508677006</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.004166276194155216</v>
+        <v>-0.004166246391832829</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.003965079784393311</v>
+        <v>-0.003965042531490326</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.003640576265752316</v>
+        <v>-0.003640556707978249</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.00332386139780283</v>
+        <v>-0.003323836252093315</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.003071962855756283</v>
+        <v>-0.003071950748562813</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.002975260838866234</v>
+        <v>-0.002975254319608212</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.002911835908889771</v>
+        <v>-0.002911829389631748</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.002765683457255363</v>
+        <v>-0.002765672281384468</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.2599999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.002567697316408157</v>
+        <v>-0.002567680552601814</v>
       </c>
       <c r="JB80" t="n">
         <v>0.02000000000000007</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.002378742210566998</v>
+        <v>-0.00237873662263155</v>
       </c>
       <c r="JB81" t="n">
         <v>0.3</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.002262231893837452</v>
+        <v>-0.002262229099869728</v>
       </c>
       <c r="JB82" t="n">
         <v>0.5799999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.00222503300756216</v>
+        <v>-0.002225028350949287</v>
       </c>
       <c r="JB83" t="n">
         <v>0.7199999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.002213777974247932</v>
+        <v>-0.002213777042925358</v>
       </c>
       <c r="JB84" t="n">
         <v>0.5799999999999998</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.002527652308344841</v>
+        <v>-0.002527646720409393</v>
       </c>
       <c r="JB85" t="n">
         <v>0.3</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.003356304951012135</v>
+        <v>-0.003356308676302433</v>
       </c>
       <c r="JB86" t="n">
         <v>0.02000000000000007</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.004439240321516991</v>
+        <v>-0.004439231939613819</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.8599999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.005383648909628391</v>
+        <v>-0.005383546464145184</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.9999999999999998</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.006494957488030195</v>
+        <v>-0.006494874600321054</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.9999999999999998</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.007154522463679314</v>
+        <v>-0.007154521532356739</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.9999999999999998</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.007391102146357298</v>
+        <v>-0.007391029037535191</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.9999999999999998</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.007536919321864843</v>
+        <v>-0.007536835968494415</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.9999999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.007521296385675669</v>
+        <v>-0.007521224673837423</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.9999999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.007311701774597168</v>
+        <v>-0.007311609573662281</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.9999999999999998</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.007117477711290121</v>
+        <v>-0.007117390632629395</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.9999999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.006799006368964911</v>
+        <v>-0.006798994261771441</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.9999999999999998</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.006469596643000841</v>
+        <v>-0.006469557527452707</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.9999999999999998</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.006149512715637684</v>
+        <v>-0.006149479653686285</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.9999999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.005935132969170809</v>
+        <v>-0.005935091059654951</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.9999999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.005555046256631613</v>
+        <v>-0.005554998759180307</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.9999999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.005537450779229403</v>
+        <v>-0.005537413991987705</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.9999999999999998</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.005824857391417027</v>
+        <v>-0.005824802909046412</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.9999999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.006007816642522812</v>
+        <v>-0.006007748655974865</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.9999999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.006147948559373617</v>
+        <v>-0.006147890817373991</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.9999999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.006127240601927042</v>
+        <v>-0.006127208471298218</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.9999999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.00593393063172698</v>
+        <v>-0.005933907814323902</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.1199999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.005631275475025177</v>
+        <v>-0.005631244275718927</v>
       </c>
       <c r="JB107" t="n">
         <v>0.16</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.00512311514467001</v>
+        <v>-0.005123063921928406</v>
       </c>
       <c r="JB108" t="n">
         <v>0.4399999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.004563000053167343</v>
+        <v>-0.004562958143651485</v>
       </c>
       <c r="JB109" t="n">
         <v>0.7199999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.00413472019135952</v>
+        <v>-0.00413469597697258</v>
       </c>
       <c r="JB110" t="n">
         <v>0.9999999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.00381704606115818</v>
+        <v>-0.003817032091319561</v>
       </c>
       <c r="JB111" t="n">
         <v>0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.003558513708412647</v>
+        <v>-0.003558504395186901</v>
       </c>
       <c r="JB112" t="n">
         <v>0.9999999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.003508126363158226</v>
+        <v>-0.003508130088448524</v>
       </c>
       <c r="JB113" t="n">
         <v>0.9999999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.003403455018997192</v>
+        <v>-0.003403451293706894</v>
       </c>
       <c r="JB114" t="n">
         <v>0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.003490455448627472</v>
+        <v>-0.003490428440272808</v>
       </c>
       <c r="JB115" t="n">
         <v>0.8599999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.003546088002622128</v>
+        <v>-0.003546072170138359</v>
       </c>
       <c r="JB116" t="n">
         <v>0.7199999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.003596251830458641</v>
+        <v>-0.003596227616071701</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.02000000000000007</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.003583973273634911</v>
+        <v>-0.00358396302908659</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.02000000000000007</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.0035344073548913</v>
+        <v>-0.003534378483891487</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.02000000000000007</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.00342289824038744</v>
+        <v>-0.003422874957323074</v>
       </c>
       <c r="JB120" t="n">
         <v>0.1199999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.003249894827604294</v>
+        <v>-0.003249865956604481</v>
       </c>
       <c r="JB121" t="n">
         <v>0.2599999999999998</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.003088707104325294</v>
+        <v>-0.003088688477873802</v>
       </c>
       <c r="JB122" t="n">
         <v>0.9999999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.002971240319311619</v>
+        <v>-0.002971230074763298</v>
       </c>
       <c r="JB123" t="n">
         <v>0.9999999999999998</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.002738972194492817</v>
+        <v>-0.002738969400525093</v>
       </c>
       <c r="JB125" t="n">
         <v>0.9999999999999996</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.002815459854900837</v>
+        <v>-0.002815454266965389</v>
       </c>
       <c r="JB126" t="n">
         <v>0.9999999999999996</v>
